--- a/reports/Debug-snowbowl-20260105/For Winter Ending (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-snowbowl-20260105/For Winter Ending (Prior Year)_Payroll_history.xlsx
@@ -31,6 +31,39 @@
     <t>D9008</t>
   </si>
   <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D9007</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
+    <t>D9000</t>
+  </si>
+  <si>
+    <t>D9009</t>
+  </si>
+  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -46,37 +79,22 @@
     <t>D7010</t>
   </si>
   <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5820</t>
-  </si>
-  <si>
-    <t>D9007</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D9000</t>
-  </si>
-  <si>
-    <t>D9009</t>
+    <t>D1010</t>
+  </si>
+  <si>
+    <t>D1500</t>
+  </si>
+  <si>
+    <t>D6721</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D9005</t>
+  </si>
+  <si>
+    <t>D9012</t>
   </si>
   <si>
     <t>D1200</t>
@@ -92,24 +110,6 @@
   </si>
   <si>
     <t>D8060</t>
-  </si>
-  <si>
-    <t>D1010</t>
-  </si>
-  <si>
-    <t>D1500</t>
-  </si>
-  <si>
-    <t>D6721</t>
-  </si>
-  <si>
-    <t>D6790</t>
-  </si>
-  <si>
-    <t>D9005</t>
-  </si>
-  <si>
-    <t>D9012</t>
   </si>
   <si>
     <t>D1100</t>
@@ -575,7 +575,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>59219.82</v>
+        <v>85580.05</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -583,7 +583,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>40349.55</v>
+        <v>23928.74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>13766.28</v>
+        <v>50299.17</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -599,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>27293.97</v>
+        <v>4704.46</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -607,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>18334.41</v>
+        <v>6727.23</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -615,7 +615,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>85580.05</v>
+        <v>401994.50</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -623,7 +623,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>23928.74</v>
+        <v>12332.01</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -631,7 +631,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>50299.17</v>
+        <v>61448.64</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -639,7 +639,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>4704.46</v>
+        <v>49360.25</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -647,7 +647,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>6727.23</v>
+        <v>220.41</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -655,7 +655,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>401994.50</v>
+        <v>186.27</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -663,7 +663,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>12332.01</v>
+        <v>59219.82</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -671,7 +671,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>61448.64</v>
+        <v>40349.55</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -679,7 +679,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>49360.25</v>
+        <v>13766.28</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -687,7 +687,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>220.41</v>
+        <v>27293.97</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>186.27</v>
+        <v>18334.41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -703,7 +703,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>148843.02</v>
+        <v>244895.08</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -711,7 +711,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>100657.00</v>
+        <v>101419.92</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -719,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>23179.03</v>
+        <v>26305.28</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -727,7 +727,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>18552.37</v>
+        <v>32408.53</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -735,7 +735,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>44755.17</v>
+        <v>659.24</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -743,7 +743,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>244895.08</v>
+        <v>7781.00</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -751,7 +751,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>101419.92</v>
+        <v>148843.02</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -759,7 +759,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>26305.28</v>
+        <v>100657.00</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -767,7 +767,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>32408.53</v>
+        <v>23179.03</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -775,7 +775,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>659.24</v>
+        <v>18552.37</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -783,7 +783,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>7781.00</v>
+        <v>44755.17</v>
       </c>
     </row>
     <row r="33" spans="1:2">
